--- a/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$ne）.xlsx
+++ b/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$ne）.xlsx
@@ -55,98 +55,92 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$ne:&lt;值&gt;}}查询，目标字段为数值型，覆盖如下数据类型：
+    <t>1、支持数值型值的数据比较
+2、返回不等于指定值的记录，返回结果集正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、支持数值型值的数据比较，且走索引和不走索引结果一致
+2、返回不等于指定值的记录，返回结果集正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、支持嵌套数组的数据比较
+2、返回不等于指定值的记录，返回结果集正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、支持嵌套数组的数据比较，且走索引和不走索引结果一致
+2、返回不等于指定值的记录，返回结果集正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、支持所有数据类型的数据比较
+2、返回不等于指定值的记录，返回结果集正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、支持所有数据类型的数据比较，且走索引和不走索引结果一致
+2、返回不等于指定值的记录，返回结果集正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ne 选择满足“字段名”的值不等于（!=）指定“值”的记录。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$ne查询，目标字段为数值型，不走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$ne查询，目标字段为数值型，走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$ne查询，目标字段为数组且元素为数值型，不走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$ne查询，目标字段为数组且元素为数值型，走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$ne查询，目标字段为非数值型，不走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$ne查询，目标字段为非数值型，走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$ne:&lt;值&gt;}})查询，目标字段为数值型，覆盖如下数据类型：
 int/long/double，且包含该类型的最大和最小边界
 指定的$ne的值覆盖每种类型的最大和最小边界
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$ne:&lt;值&gt;}}查询，目标字段为数值型，且为索引字段，覆盖如下数据类型：
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$ne:&lt;值&gt;}})查询，目标字段为数值型，且为索引字段，覆盖如下数据类型：
 int/long/double，且包含该类型的最大和最小边界
 指定的$ne的值覆盖每种类型的最大和最小边界
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$ne:&lt;值&gt;}}查询，目标字段为嵌套数组，数组元素包含数值型（int/long/double），$ne指定的字段名为"a"或"a.b"表示
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$ne:&lt;值&gt;}})查询，目标字段为嵌套数组，数组元素包含数值型（int/long/double），$ne指定的字段名为"a"或"a.b"表示
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$ne:&lt;值&gt;}}查询，目标字段为嵌套数组，且为索引字段，数组元素包含数值型（int/long/double），$ne指定的字段名为"a"或"a.b"表示
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$ne:&lt;值&gt;}})查询，目标字段为嵌套数组，且为索引字段，数组元素包含数值型（int/long/double），$ne指定的字段名为"a"或"a.b"表示
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$ne:&lt;值&gt;}}查询，目标字段为非数值型，覆盖其他所有非数值型数据：
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$ne:&lt;值&gt;}})查询，目标字段为非数值型，覆盖其他所有非数值型数据：
 null, string, bool, array, oid, date, binary, regex, timestamp, minKey, maxKey, subobj
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$ne:&lt;值&gt;}}查询，目标字段为非数值型，且为索引字段，覆盖其他所有非数值型数据：
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$ne:&lt;值&gt;}})查询，目标字段为非数值型，且为索引字段，覆盖其他所有非数值型数据：
 null, string, bool, array, oid, date, binary, regex, timestamp, minKey, maxKey, subobj
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、支持数值型值的数据比较
-2、返回不等于指定值的记录，返回结果集正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、支持数值型值的数据比较，且走索引和不走索引结果一致
-2、返回不等于指定值的记录，返回结果集正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、支持嵌套数组的数据比较
-2、返回不等于指定值的记录，返回结果集正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、支持嵌套数组的数据比较，且走索引和不走索引结果一致
-2、返回不等于指定值的记录，返回结果集正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、支持所有数据类型的数据比较
-2、返回不等于指定值的记录，返回结果集正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、支持所有数据类型的数据比较，且走索引和不走索引结果一致
-2、返回不等于指定值的记录，返回结果集正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>$ne 选择满足“字段名”的值不等于（!=）指定“值”的记录。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$ne查询，目标字段为数值型，不走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$ne查询，目标字段为数值型，走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$ne查询，目标字段为数组且元素为数值型，不走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$ne查询，目标字段为数组且元素为数值型，走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$ne查询，目标字段为非数值型，不走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$ne查询，目标字段为非数值型，走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -669,10 +663,10 @@
     </row>
     <row r="2" spans="1:9" ht="67.5">
       <c r="A2" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -687,10 +681,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
@@ -698,7 +692,7 @@
     </row>
     <row r="3" spans="1:9" ht="67.5">
       <c r="A3" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -713,10 +707,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
@@ -724,7 +718,7 @@
     </row>
     <row r="4" spans="1:9" ht="54">
       <c r="A4" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
@@ -739,10 +733,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -750,7 +744,7 @@
     </row>
     <row r="5" spans="1:9" ht="67.5">
       <c r="A5" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -765,10 +759,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -776,7 +770,7 @@
     </row>
     <row r="6" spans="1:9" ht="67.5">
       <c r="A6" s="6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
@@ -791,10 +785,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -802,7 +796,7 @@
     </row>
     <row r="7" spans="1:9" ht="67.5">
       <c r="A7" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -817,10 +811,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
